--- a/artifacts/reports/architecture_tuning_mlp_v1.xlsx
+++ b/artifacts/reports/architecture_tuning_mlp_v1.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03024068400944949</v>
+        <v>0.02995315914280258</v>
       </c>
     </row>
     <row r="14">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.129013591620605</v>
+        <v>5.144218712503061</v>
       </c>
     </row>
     <row r="16">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.963978400104679</v>
+        <v>5.032344750004995</v>
       </c>
     </row>
     <row r="17">
@@ -850,7 +850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AJ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -916,85 +916,120 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>hidden_size</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>num_layers</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>dropout</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>train_r</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>r_min</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>r_max</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>hidden_dims</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>depth</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>params_json</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>params_repr</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>n_series</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>horizon</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>mae_mean</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>rmse_mean</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>mase_mean</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>directional_accuracy_mean</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>fit_time_sec_mean</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>predict_time_sec_mean</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>fit_time</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>predict_time</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>total_runtime_sec</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -1003,7 +1038,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1029,68 +1064,75 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
         <is>
           <t>[32]</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="U2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_001", "model_params": {"hidden_dims": [32], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [32], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_001'}</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="X2" t="n">
         <v>12</v>
       </c>
-      <c r="R2" t="n">
+      <c r="Y2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
+      <c r="Z2" t="n">
         <v>0.01072247167885253</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AA2" t="n">
         <v>0.01469807419688153</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AB2" t="n">
         <v>0.7156893566600132</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AC2" t="n">
         <v>0.4880933207046982</v>
       </c>
-      <c r="W2" t="n">
-        <v>0.153453125003984</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.0002930611113293304</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.153453125003984</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.0002930611113293304</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>5.53486270015128</v>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>0.1521615388923641</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.0002695027788932849</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.1521615388923641</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.0002695027788932849</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>5.487517500165268</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1116,68 +1158,75 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
         <is>
           <t>[32]</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="U3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_001", "model_params": {"hidden_dims": [32], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [32], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_001'}</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="X3" t="n">
         <v>12</v>
       </c>
-      <c r="R3" t="n">
+      <c r="Y3" t="n">
         <v>5</v>
       </c>
-      <c r="S3" t="n">
-        <v>0.02456737190194523</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.03262874238861787</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.696275800026964</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.5055849859178333</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.1166104361214416</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.0002343833330087364</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.1166104361214416</v>
-      </c>
       <c r="Z3" t="n">
-        <v>0.0002343833330087364</v>
+        <v>0.02448791935763095</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.206413500360213</v>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>0.03257416298744947</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.692305675970661</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5067610823093516</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.1110188138894349</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.000200808332010638</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.1110188138894349</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.000200808332010638</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>4.003906399972038</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1203,68 +1252,75 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
         <is>
           <t>[32]</t>
         </is>
       </c>
-      <c r="N4" t="n">
+      <c r="U4" t="n">
         <v>1</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_001", "model_params": {"hidden_dims": [32], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [32], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_001'}</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="X4" t="n">
         <v>12</v>
       </c>
-      <c r="R4" t="n">
+      <c r="Y4" t="n">
         <v>20</v>
       </c>
-      <c r="S4" t="n">
-        <v>0.05232339618499738</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.06636460245640763</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.537095816706637</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.5211862460254756</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.1099124416650739</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.0002185194332721747</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.1099124416650739</v>
-      </c>
       <c r="Z4" t="n">
-        <v>0.0002185194332721747</v>
+        <v>0.05144940030813321</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.964714599540457</v>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>0.0651977572190537</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>3.488342556390577</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.5243300639708162</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.1031370444454499</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.0001979555579762544</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.1031370444454499</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.0001979555579762544</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>3.72006000012334</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1290,68 +1346,75 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
         <is>
           <t>[64]</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_002", "model_params": {"hidden_dims": [64], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [64], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_002'}</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="X5" t="n">
         <v>12</v>
       </c>
-      <c r="R5" t="n">
+      <c r="Y5" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
+      <c r="Z5" t="n">
         <v>0.01219898962171133</v>
       </c>
-      <c r="T5" t="n">
+      <c r="AA5" t="n">
         <v>0.01615075364854835</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AB5" t="n">
         <v>0.9004564654860455</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AC5" t="n">
         <v>0.4823874694801014</v>
       </c>
-      <c r="W5" t="n">
-        <v>0.1299787944460857</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.0002596666648363073</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.1299787944460857</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.0002596666648363073</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4.688584599993192</v>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>0.124177816665906</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.0002477166668136811</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.124177816665906</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.0002477166668136811</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>4.479319199977908</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1377,68 +1440,75 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
         <is>
           <t>[64]</t>
         </is>
       </c>
-      <c r="N6" t="n">
+      <c r="U6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_002", "model_params": {"hidden_dims": [64], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [64], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_002'}</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="X6" t="n">
         <v>12</v>
       </c>
-      <c r="R6" t="n">
+      <c r="Y6" t="n">
         <v>5</v>
       </c>
-      <c r="S6" t="n">
-        <v>0.02788304199056224</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.03592350682022432</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.201611692266755</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.5020736003117062</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.1251406583404686</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.0002332194384911822</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.1251406583404686</v>
-      </c>
       <c r="Z6" t="n">
-        <v>0.0002332194384911822</v>
+        <v>0.02799804960697496</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.513459600042552</v>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+        <v>0.03607063490726811</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.217446829727454</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.5032429721366207</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.1161902500005251</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.0002168638889593745</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.1161902500005251</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.0002168638889593745</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>4.190656100021442</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1464,68 +1534,75 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
         <is>
           <t>[64]</t>
         </is>
       </c>
-      <c r="N7" t="n">
+      <c r="U7" t="n">
         <v>1</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_002", "model_params": {"hidden_dims": [64], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [64], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_002'}</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="X7" t="n">
         <v>12</v>
       </c>
-      <c r="R7" t="n">
+      <c r="Y7" t="n">
         <v>20</v>
       </c>
-      <c r="S7" t="n">
-        <v>0.04911705400657308</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.0627768925027352</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.227436265379421</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.5097054528584869</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.1061215805594758</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.0002306638925801963</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.1061215805594758</v>
-      </c>
       <c r="Z7" t="n">
-        <v>0.0002306638925801963</v>
+        <v>0.04857608308911196</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.828680800274014</v>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>0.06227722278622067</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.180593188474799</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5127018130873311</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.09950939444267232</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.0002125555567747344</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.09950939444267232</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.0002125555567747344</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>3.589990199980093</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1551,68 +1628,75 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
         <is>
           <t>[64, 32]</t>
         </is>
       </c>
-      <c r="N8" t="n">
+      <c r="U8" t="n">
         <v>2</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_003", "model_params": {"hidden_dims": [64, 32], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [64, 32], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_003'}</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="X8" t="n">
         <v>12</v>
       </c>
-      <c r="R8" t="n">
+      <c r="Y8" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="n">
+      <c r="Z8" t="n">
         <v>0.01038002895300485</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AA8" t="n">
         <v>0.01433854003613678</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AB8" t="n">
         <v>0.6809677930376198</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AC8" t="n">
         <v>0.4969121113001507</v>
       </c>
-      <c r="W8" t="n">
-        <v>0.1291877249863723</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.000344655570289534</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.1291877249863723</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.000344655570289534</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4.663165700039826</v>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="n">
+        <v>0.1276401555551274</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.0003187611109751743</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.1276401555551274</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.0003187611109751743</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>4.606520999979693</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1638,68 +1722,75 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
         <is>
           <t>[64, 32]</t>
         </is>
       </c>
-      <c r="N9" t="n">
+      <c r="U9" t="n">
         <v>2</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_003", "model_params": {"hidden_dims": [64, 32], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [64, 32], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_003'}</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="X9" t="n">
         <v>12</v>
       </c>
-      <c r="R9" t="n">
+      <c r="Y9" t="n">
         <v>5</v>
       </c>
-      <c r="S9" t="n">
-        <v>0.02810029230972147</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.0360163117210615</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.283026527559965</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.5143450946520943</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.1409445000042777</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.0003201916794447849</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.1409445000042777</v>
-      </c>
       <c r="Z9" t="n">
-        <v>0.0003201916794447849</v>
+        <v>0.02825361309357463</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.085528900614008</v>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>0.03620671298628976</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.299023272309361</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.5134938056000219</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.138469611111456</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.0003130500000325911</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.138469611111456</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.0003130500000325911</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>4.996175800013589</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1725,68 +1816,75 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
         <is>
           <t>[64, 32]</t>
         </is>
       </c>
-      <c r="N10" t="n">
+      <c r="U10" t="n">
         <v>2</v>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_003", "model_params": {"hidden_dims": [64, 32], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [64, 32], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_003'}</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="X10" t="n">
         <v>12</v>
       </c>
-      <c r="R10" t="n">
+      <c r="Y10" t="n">
         <v>20</v>
       </c>
-      <c r="S10" t="n">
-        <v>0.05108379759057149</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.06453507559689452</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3.428227930907022</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.5162117913868376</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.125424516652452</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.0003368361083428478</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.125424516652452</v>
-      </c>
       <c r="Z10" t="n">
-        <v>0.0003368361083428478</v>
+        <v>0.05045955534090029</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.527408699388616</v>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr"/>
+        <v>0.06392335096386302</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.3733239112577</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.5167157149408247</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.1204945250000391</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.0002903583327780426</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.1204945250000391</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.0002903583327780426</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>4.348255799981416</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1812,68 +1910,75 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
         <is>
           <t>[128, 64]</t>
         </is>
       </c>
-      <c r="N11" t="n">
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_004", "model_params": {"hidden_dims": [128, 64], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [128, 64], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_004'}</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="X11" t="n">
         <v>12</v>
       </c>
-      <c r="R11" t="n">
+      <c r="Y11" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="Z11" t="n">
         <v>0.01052181117208291</v>
       </c>
-      <c r="T11" t="n">
+      <c r="AA11" t="n">
         <v>0.01445988522803084</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AB11" t="n">
         <v>0.6864935691213873</v>
       </c>
-      <c r="V11" t="n">
+      <c r="AC11" t="n">
         <v>0.4940635947797116</v>
       </c>
-      <c r="W11" t="n">
-        <v>0.1426138138793047</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.0004241777771514737</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.1426138138793047</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.0004241777771514737</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>5.149367699632421</v>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>0.1484772222247557</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.0003998361090553873</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.1484772222247557</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.0003998361090553873</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>5.359574100017198</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1899,68 +2004,75 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
         <is>
           <t>[128, 64]</t>
         </is>
       </c>
-      <c r="N12" t="n">
+      <c r="U12" t="n">
         <v>2</v>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_004", "model_params": {"hidden_dims": [128, 64], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [128, 64], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_004'}</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="X12" t="n">
         <v>12</v>
       </c>
-      <c r="R12" t="n">
+      <c r="Y12" t="n">
         <v>5</v>
       </c>
-      <c r="S12" t="n">
-        <v>0.02312079830273001</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.03112126018347533</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.526712362491778</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.5213691326413427</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.1373086583399628</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.0003594333215409683</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.1373086583399628</v>
-      </c>
       <c r="Z12" t="n">
-        <v>0.0003594333215409683</v>
+        <v>0.02315534169197575</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.956051299814135</v>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr"/>
+        <v>0.03118980958739329</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.529759097644589</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.5229966183750273</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.1404280888891662</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.0003639583329560184</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.1404280888891662</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.0003639583329560184</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>5.068513699996402</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1986,68 +2098,75 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
         <is>
           <t>[128, 64]</t>
         </is>
       </c>
-      <c r="N13" t="n">
+      <c r="U13" t="n">
         <v>2</v>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_004", "model_params": {"hidden_dims": [128, 64], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [128, 64], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_004'}</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="X13" t="n">
         <v>12</v>
       </c>
-      <c r="R13" t="n">
+      <c r="Y13" t="n">
         <v>20</v>
       </c>
-      <c r="S13" t="n">
-        <v>0.04696464614703105</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.0602590925533735</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.034328669224048</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.5114099551166897</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.120266286112989</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.0007812222142496869</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.120266286112989</v>
-      </c>
       <c r="Z13" t="n">
-        <v>0.0007812222142496869</v>
+        <v>0.0459809436903356</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.357710299780592</v>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr"/>
+        <v>0.05912130603274527</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.975150672680173</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.5370551052210905</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.1087836499997745</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.000337127775613529</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.1087836499997745</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.000337127775613529</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>3.928347999913967</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2073,68 +2192,75 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
         <is>
           <t>[32]</t>
         </is>
       </c>
-      <c r="N14" t="n">
+      <c r="U14" t="n">
         <v>1</v>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_001", "model_params": {"hidden_dims": [32], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [32], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_001'}</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="X14" t="n">
         <v>12</v>
       </c>
-      <c r="R14" t="n">
+      <c r="Y14" t="n">
         <v>1</v>
       </c>
-      <c r="S14" t="n">
+      <c r="Z14" t="n">
         <v>0.01537355039475501</v>
       </c>
-      <c r="T14" t="n">
+      <c r="AA14" t="n">
         <v>0.01916780226021344</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AB14" t="n">
         <v>1.288271222465976</v>
       </c>
-      <c r="V14" t="n">
+      <c r="AC14" t="n">
         <v>0.4843472493382439</v>
       </c>
-      <c r="W14" t="n">
-        <v>0.1427457555514088</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.0003896222171735847</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.1427457555514088</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.0003896222171735847</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>5.152873599668965</v>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="n">
+        <v>0.1486269888894943</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.0004324805550923985</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.1486269888894943</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.0004324805550923985</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>5.366140900005121</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2160,68 +2286,75 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
         <is>
           <t>[32]</t>
         </is>
       </c>
-      <c r="N15" t="n">
+      <c r="U15" t="n">
         <v>1</v>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_001", "model_params": {"hidden_dims": [32], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [32], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_001'}</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="X15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" t="n">
+      <c r="Y15" t="n">
         <v>5</v>
       </c>
-      <c r="S15" t="n">
-        <v>0.02555454382818369</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.03361677745866084</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.896482281938239</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.520094432774746</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.1344480777754345</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.0003762999969896756</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.1344480777754345</v>
-      </c>
       <c r="Z15" t="n">
-        <v>0.0003762999969896756</v>
+        <v>0.02561282455113349</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.85367759980727</v>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr"/>
+        <v>0.03366521448181965</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.905864278934198</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.5207234562608192</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.1380107777780116</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.0003933499994875295</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.1380107777780116</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.0003933499994875295</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>4.982548599989968</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2247,68 +2380,75 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
         <is>
           <t>[32]</t>
         </is>
       </c>
-      <c r="N16" t="n">
+      <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_001", "model_params": {"hidden_dims": [32], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [32], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_001'}</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="X16" t="n">
         <v>12</v>
       </c>
-      <c r="R16" t="n">
+      <c r="Y16" t="n">
         <v>20</v>
       </c>
-      <c r="S16" t="n">
-        <v>0.05910786074489652</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.07239385309033819</v>
-      </c>
-      <c r="U16" t="n">
-        <v>4.301406358458906</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.5091649891459007</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.1326071138836495</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.000382866668385557</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.1326071138836495</v>
-      </c>
       <c r="Z16" t="n">
-        <v>0.000382866668385557</v>
+        <v>0.05687098935334142</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.787639299873263</v>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr"/>
+        <v>0.0701598830308772</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>4.118561749280627</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.5393439010470117</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.1333680055560965</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.0003959138905176789</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.1333680055560965</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.0003959138905176789</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>4.815501100078109</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2334,68 +2474,75 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
         <is>
           <t>[64]</t>
         </is>
       </c>
-      <c r="N17" t="n">
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_002", "model_params": {"hidden_dims": [64], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [64], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_002'}</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="X17" t="n">
         <v>12</v>
       </c>
-      <c r="R17" t="n">
+      <c r="Y17" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
+      <c r="Z17" t="n">
         <v>0.01045530521320673</v>
       </c>
-      <c r="T17" t="n">
+      <c r="AA17" t="n">
         <v>0.01439863498542497</v>
       </c>
-      <c r="U17" t="n">
+      <c r="AB17" t="n">
         <v>0.6839026086444736</v>
       </c>
-      <c r="V17" t="n">
+      <c r="AC17" t="n">
         <v>0.4973883114027627</v>
       </c>
-      <c r="W17" t="n">
-        <v>0.1376431638847053</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.0004653222373841952</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.1376431638847053</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0.0004653222373841952</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.971905500395223</v>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="n">
+        <v>0.1619814250002997</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.000565719444340276</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.1619814250002997</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.000565719444340276</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>5.851697200007038</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2421,68 +2568,75 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
         <is>
           <t>[64]</t>
         </is>
       </c>
-      <c r="N18" t="n">
+      <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_002", "model_params": {"hidden_dims": [64], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [64], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_002'}</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="X18" t="n">
         <v>12</v>
       </c>
-      <c r="R18" t="n">
+      <c r="Y18" t="n">
         <v>5</v>
       </c>
-      <c r="S18" t="n">
-        <v>0.0361036796977896</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.04416617028589526</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3.390239976476728</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.5074238083082002</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.1466672222272286</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.0004016861106113841</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.1466672222272286</v>
-      </c>
       <c r="Z18" t="n">
-        <v>0.0004016861106113841</v>
+        <v>0.03629588854131685</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.294480700162239</v>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr"/>
+        <v>0.04434808007922147</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>3.432064737504424</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.5074808624640675</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.1686749972234086</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.0004970916658445882</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.1686749972234086</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.0004970916658445882</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>6.090195200013113</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2508,68 +2662,75 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
         <is>
           <t>[64]</t>
         </is>
       </c>
-      <c r="N19" t="n">
+      <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_002", "model_params": {"hidden_dims": [64], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [64], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_002'}</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="X19" t="n">
         <v>12</v>
       </c>
-      <c r="R19" t="n">
+      <c r="Y19" t="n">
         <v>20</v>
       </c>
-      <c r="S19" t="n">
-        <v>0.05480327587566839</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.06826982847447428</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3.500363507500051</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.5512072206730737</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0.1260809527852366</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0.0003779472155858658</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.1260809527852366</v>
-      </c>
       <c r="Z19" t="n">
-        <v>0.0003779472155858658</v>
+        <v>0.05406039255051812</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.552520400029607</v>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr"/>
+        <v>0.06752580573523297</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.38392458821367</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.5540783871802364</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.1376522888903209</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.0004507305550052681</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.1376522888903209</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.0004507305550052681</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>4.971708700031741</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2595,68 +2756,75 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
         <is>
           <t>[64, 32]</t>
         </is>
       </c>
-      <c r="N20" t="n">
+      <c r="U20" t="n">
         <v>2</v>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_003", "model_params": {"hidden_dims": [64, 32], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [64, 32], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_003'}</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="X20" t="n">
         <v>12</v>
       </c>
-      <c r="R20" t="n">
+      <c r="Y20" t="n">
         <v>1</v>
       </c>
-      <c r="S20" t="n">
+      <c r="Z20" t="n">
         <v>0.01467755137442022</v>
       </c>
-      <c r="T20" t="n">
+      <c r="AA20" t="n">
         <v>0.01850024212165555</v>
       </c>
-      <c r="U20" t="n">
+      <c r="AB20" t="n">
         <v>1.206688935910835</v>
       </c>
-      <c r="V20" t="n">
+      <c r="AC20" t="n">
         <v>0.4933989554493118</v>
       </c>
-      <c r="W20" t="n">
-        <v>0.1748512333271921</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0.0006741666745963609</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.1748512333271921</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0.0006741666745963609</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>6.318914400064386</v>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="n">
+        <v>0.1734516722224524</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.0006575722194005116</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.1734516722224524</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.0006575722194005116</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>6.267932799906703</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2682,68 +2850,75 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
         <is>
           <t>[64, 32]</t>
         </is>
       </c>
-      <c r="N21" t="n">
+      <c r="U21" t="n">
         <v>2</v>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_003", "model_params": {"hidden_dims": [64, 32], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [64, 32], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_003'}</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="X21" t="n">
         <v>12</v>
       </c>
-      <c r="R21" t="n">
+      <c r="Y21" t="n">
         <v>5</v>
       </c>
-      <c r="S21" t="n">
-        <v>0.0232369414225978</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.03123330355526041</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.547567934110495</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0.5253092070363823</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0.1698220055550337</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0.0006668138990385664</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0.1698220055550337</v>
-      </c>
       <c r="Z21" t="n">
-        <v>0.0006668138990385664</v>
+        <v>0.02358033022153232</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.137597500346601</v>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr"/>
+        <v>0.03164320348905051</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.579655701468333</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.5163589882272985</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.159773927777375</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.0006147999989075793</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.159773927777375</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.0006147999989075793</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>5.773994199946173</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2769,68 +2944,75 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
         <is>
           <t>[64, 32]</t>
         </is>
       </c>
-      <c r="N22" t="n">
+      <c r="U22" t="n">
         <v>2</v>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_003", "model_params": {"hidden_dims": [64, 32], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [64, 32], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_003'}</t>
         </is>
       </c>
-      <c r="Q22" t="n">
+      <c r="X22" t="n">
         <v>12</v>
       </c>
-      <c r="R22" t="n">
+      <c r="Y22" t="n">
         <v>20</v>
       </c>
-      <c r="S22" t="n">
-        <v>0.04820975959035242</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.06145056888114758</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3.120485363022373</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0.5384502808899151</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0.1610922361012652</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0.000571797223528847</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0.1610922361012652</v>
-      </c>
       <c r="Z22" t="n">
-        <v>0.000571797223528847</v>
+        <v>0.04766625080047376</v>
       </c>
       <c r="AA22" t="n">
-        <v>5.819905199692585</v>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr"/>
+        <v>0.06094719349158497</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>3.075976975236062</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.5264311397016285</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.1577999611104638</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.0006298527773146311</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.1577999611104638</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.0006298527773146311</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>5.703473299960024</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2856,68 +3038,75 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
         <is>
           <t>[128, 64]</t>
         </is>
       </c>
-      <c r="N23" t="n">
+      <c r="U23" t="n">
         <v>2</v>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_004", "model_params": {"hidden_dims": [128, 64], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [128, 64], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_004'}</t>
         </is>
       </c>
-      <c r="Q23" t="n">
+      <c r="X23" t="n">
         <v>12</v>
       </c>
-      <c r="R23" t="n">
+      <c r="Y23" t="n">
         <v>1</v>
       </c>
-      <c r="S23" t="n">
+      <c r="Z23" t="n">
         <v>0.0161231616822145</v>
       </c>
-      <c r="T23" t="n">
+      <c r="AA23" t="n">
         <v>0.01985140375065752</v>
       </c>
-      <c r="U23" t="n">
+      <c r="AB23" t="n">
         <v>1.37542400433574</v>
       </c>
-      <c r="V23" t="n">
+      <c r="AC23" t="n">
         <v>0.4766717094139015</v>
       </c>
-      <c r="W23" t="n">
-        <v>0.1856918027721501</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0.0007341499925435832</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0.1856918027721501</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0.0007341499925435832</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>6.711334299528971</v>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="n">
+        <v>0.1924067555547582</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.0007077638882846158</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.1924067555547582</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.0007077638882846158</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>6.952122699949541</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2943,68 +3132,75 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
         <is>
           <t>[128, 64]</t>
         </is>
       </c>
-      <c r="N24" t="n">
+      <c r="U24" t="n">
         <v>2</v>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_004", "model_params": {"hidden_dims": [128, 64], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [128, 64], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_004'}</t>
         </is>
       </c>
-      <c r="Q24" t="n">
+      <c r="X24" t="n">
         <v>12</v>
       </c>
-      <c r="R24" t="n">
+      <c r="Y24" t="n">
         <v>5</v>
       </c>
-      <c r="S24" t="n">
-        <v>0.0239645154046154</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.03193452078389262</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.616566447937623</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0.4969784000448509</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0.1814445833410395</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0.0007391277661857506</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0.1814445833410395</v>
-      </c>
       <c r="Z24" t="n">
-        <v>0.0007391277661857506</v>
+        <v>0.02371184149353015</v>
       </c>
       <c r="AA24" t="n">
-        <v>6.558613599860109</v>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr"/>
+        <v>0.03173798517987021</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.605736105164391</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.5038017354222256</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.1837537361114099</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.0006922694430815885</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.1837537361114099</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.0006922694430815885</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>6.640056199961691</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3030,63 +3226,70 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr">
         <is>
           <t>[128, 64]</t>
         </is>
       </c>
-      <c r="N25" t="n">
+      <c r="U25" t="n">
         <v>2</v>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>{"compare_group_id": "mlp_grp_004", "model_params": {"hidden_dims": [128, 64], "seed": 2026}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_dims': [128, 64], 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'mlp_grp_004'}</t>
         </is>
       </c>
-      <c r="Q25" t="n">
+      <c r="X25" t="n">
         <v>12</v>
       </c>
-      <c r="R25" t="n">
+      <c r="Y25" t="n">
         <v>20</v>
       </c>
-      <c r="S25" t="n">
-        <v>0.0511825711383037</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.06471676938250173</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3.334439013417954</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0.5130398352860598</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0.1787758055498772</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0.0006940750010673784</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0.1787758055498772</v>
-      </c>
       <c r="Z25" t="n">
-        <v>0.0006940750010673784</v>
+        <v>0.05026352564653038</v>
       </c>
       <c r="AA25" t="n">
-        <v>6.460915699834004</v>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr"/>
+        <v>0.06365448108769543</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>3.287206308415527</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.5202115598301923</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.1734004694452677</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.0006839861125627067</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.1734004694452677</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.0006839861125627067</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>6.267040400081896</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3181,10 +3384,10 @@
         <v>0.4973883114027627</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1376431638847053</v>
+        <v>0.1619814250002997</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0004653222373841952</v>
+        <v>0.000565719444340276</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -3207,22 +3410,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.0232369414225978</v>
+        <v>0.02358033022153232</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03123330355526041</v>
+        <v>0.03164320348905051</v>
       </c>
       <c r="F3" t="n">
-        <v>1.547567934110495</v>
+        <v>1.579655701468333</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5253092070363823</v>
+        <v>0.5163589882272985</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1698220055550337</v>
+        <v>0.159773927777375</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006668138990385664</v>
+        <v>0.0006147999989075793</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -3245,22 +3448,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04820975959035242</v>
+        <v>0.04766625080047376</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06145056888114758</v>
+        <v>0.06094719349158497</v>
       </c>
       <c r="F4" t="n">
-        <v>3.120485363022373</v>
+        <v>3.075976975236062</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5384502808899151</v>
+        <v>0.5264311397016285</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1610922361012652</v>
+        <v>0.1577999611104638</v>
       </c>
       <c r="I4" t="n">
-        <v>0.000571797223528847</v>
+        <v>0.0006298527773146311</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -3295,10 +3498,10 @@
         <v>0.4969121113001507</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1291877249863723</v>
+        <v>0.1276401555551274</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000344655570289534</v>
+        <v>0.0003187611109751743</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -3321,22 +3524,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.02312079830273001</v>
+        <v>0.02315534169197575</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03112126018347533</v>
+        <v>0.03118980958739329</v>
       </c>
       <c r="F6" t="n">
-        <v>1.526712362491778</v>
+        <v>1.529759097644589</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5213691326413427</v>
+        <v>0.5229966183750273</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1373086583399628</v>
+        <v>0.1404280888891662</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003594333215409683</v>
+        <v>0.0003639583329560184</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -3359,22 +3562,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.04696464614703105</v>
+        <v>0.0459809436903356</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0602590925533735</v>
+        <v>0.05912130603274527</v>
       </c>
       <c r="F7" t="n">
-        <v>3.034328669224048</v>
+        <v>2.975150672680173</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5114099551166897</v>
+        <v>0.5370551052210905</v>
       </c>
       <c r="H7" t="n">
-        <v>0.120266286112989</v>
+        <v>0.1087836499997745</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007812222142496869</v>
+        <v>0.000337127775613529</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -3393,7 +3596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:AL13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3414,82 +3617,1401 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>base_model_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>chaotic_model_name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>secondary_model_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>base_candidate_id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>chaotic_candidate_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>secondary_candidate_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>base_mae_mean</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>chaotic_mae_mean</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>secondary_mae_mean</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>chaotic_delta_mae_vs_base</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>secondary_delta_mae_vs_base</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>base_runtime_sec_mean</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>chaotic_runtime_sec_mean</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>secondary_runtime_sec_mean</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>chaotic_runtime_delta_sec_vs_base</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>secondary_runtime_delta_sec_vs_base</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>base_status</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>chaotic_status</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>secondary_status</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>esn_candidate_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>chaotic_esn_candidate_id</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_candidate_id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>esn_mae_mean</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>chaotic_esn_mae_mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_mae_mean</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>chaotic_esn_delta_mae_vs_esn</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_delta_mae_vs_esn</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>esn_runtime_sec_mean</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>chaotic_esn_runtime_sec_mean</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_runtime_sec_mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>chaotic_esn_runtime_delta_sec_vs_esn</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_runtime_delta_sec_vs_esn</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>esn_status</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>chaotic_esn_status</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>mlp_grp_001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>vanilla_mlp</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>chaotic_mlp</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>vanilla_mlp_g001</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>chaotic_mlp_g001</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>0.01072247167885253</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.01537355039475501</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>0.004651078715902479</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0.1524310416712574</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1490594694445867</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>-0.003371572226670727</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>mlp_grp_002</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>vanilla_mlp</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>chaotic_mlp</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>vanilla_mlp_g002</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>chaotic_mlp_g002</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>0.01219898962171133</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.01045530521320673</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>-0.001743684408504594</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0.1244255333327197</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.1625471444446399</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>0.03812161111192028</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>mlp_grp_003</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>vanilla_mlp</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>chaotic_mlp</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>vanilla_mlp_g003</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>chaotic_mlp_g003</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>0.01038002895300485</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.01467755137442022</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>0.004297522421415364</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0.1279589166661026</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1741092444418529</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>0.04615032777575029</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>mlp_grp_004</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>vanilla_mlp</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>chaotic_mlp</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>vanilla_mlp_g004</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>chaotic_mlp_g004</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0.01052181117208291</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0161231616822145</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>0.005601350510131586</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>0.1488770583338111</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1931145194430428</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>0.04423746110923174</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mlp_grp_001</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>vanilla_mlp</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>chaotic_mlp</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>vanilla_mlp_g001</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>chaotic_mlp_g001</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>0.02448791935763095</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.02561282455113349</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0.001124905193502539</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>0.1112196222214455</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1384041277774991</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>0.0271845055560536</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mlp_grp_002</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>vanilla_mlp</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>chaotic_mlp</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>vanilla_mlp_g002</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>chaotic_mlp_g002</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>0.02799804960697496</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.03629588854131685</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>0.008297838934341894</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>0.1164071138894845</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1691720888892532</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>0.05276497499976868</v>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>mlp_grp_003</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>vanilla_mlp</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>chaotic_mlp</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>vanilla_mlp_g003</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>chaotic_mlp_g003</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>0.02825361309357463</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.02358033022153232</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>-0.004673282872042314</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>0.1387826611114886</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.1603887277762826</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>0.021606066664794</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mlp_grp_004</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>vanilla_mlp</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>chaotic_mlp</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>vanilla_mlp_g004</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>chaotic_mlp_g004</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>0.02315534169197575</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02371184149353015</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>0.0005564998015544012</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>0.1407920472221222</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.1844460055544914</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>0.04365395833236921</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>mlp_grp_001</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>vanilla_mlp</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>chaotic_mlp</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>vanilla_mlp_g001</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>chaotic_mlp_g001</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>0.05144940030813321</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.05687098935334142</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>0.005421589045208203</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>0.1033350000034261</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.1337639194466142</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>0.03042891944318807</v>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mlp_grp_002</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>vanilla_mlp</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>chaotic_mlp</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>vanilla_mlp_g002</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>chaotic_mlp_g002</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>0.04857608308911196</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.05406039255051812</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>0.005484309461406156</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>0.09972194999944706</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.1381030194453261</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>0.03838106944587907</v>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>mlp_grp_003</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>vanilla_mlp</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>chaotic_mlp</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>vanilla_mlp_g003</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>chaotic_mlp_g003</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>0.05045955534090029</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.04766625080047376</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>-0.002793304540426533</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>0.1207848833328171</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.1584298138877785</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>0.03764493055496133</v>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mlp_grp_004</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>vanilla_mlp</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>chaotic_mlp</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>vanilla_mlp_g004</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>chaotic_mlp_g004</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>0.0459809436903356</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.05026352564653038</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>0.004282581956194784</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>0.109120777775388</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.1740844555578304</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>0.06496367778244247</v>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>missing</t>
         </is>
       </c>
     </row>
@@ -3572,7 +5094,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3586,25 +5108,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.02870808412912348</v>
+        <v>0.02864137746547543</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03706137151935451</v>
+        <v>0.03703021303409701</v>
       </c>
       <c r="F2" t="n">
-        <v>1.958247411014568</v>
+        <v>1.954107204205077</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5190528144585365</v>
+        <v>0.5120630277927463</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1685884916611637</v>
+        <v>0.1636751870367637</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0006375925990545914</v>
+        <v>0.0006340749985409073</v>
       </c>
       <c r="J2" t="n">
-        <v>6.092139033367857</v>
+        <v>5.915133433270967</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3620,7 +5142,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3634,25 +5156,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.02686908520728132</v>
+        <v>0.02655269885146476</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03528007932162656</v>
+        <v>0.0349236669493898</v>
       </c>
       <c r="F3" t="n">
-        <v>1.749178200279071</v>
+        <v>1.730467779815383</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5089475608459146</v>
+        <v>0.5180384394586098</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1333962527774188</v>
+        <v>0.1325629870378988</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000521611104314043</v>
+        <v>0.0003669740725416449</v>
       </c>
       <c r="J3" t="n">
-        <v>4.821043099742383</v>
+        <v>4.785478599975856</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3699,7 +5221,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>architecture_tuning_mlp_v1_20260329T162757Z</t>
+          <t>architecture_tuning_mlp_v1_20260819T071014Z</t>
         </is>
       </c>
     </row>
